--- a/search-a-sort-analyza Oliver Komka.xlsx
+++ b/search-a-sort-analyza Oliver Komka.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A781F54C-4BFA-4948-B135-9293E288C598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8C9321-E18B-4E7B-8FFC-A89B87078CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Search" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="49">
   <si>
     <t>Linear Search O(N)</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t xml:space="preserve">	822.44</t>
+  </si>
+  <si>
+    <t>O(n log n)</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1312,6 +1315,19 @@
     <xf numFmtId="4" fontId="15" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1377,21 +1393,6 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9424,20 +9425,20 @@
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:14" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E5" s="103" t="s">
+      <c r="E5" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="103" t="s">
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="105"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="112"/>
     </row>
     <row r="6" spans="2:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="2" t="s">
@@ -9475,7 +9476,7 @@
       </c>
     </row>
     <row r="7" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="102">
+      <c r="B7" s="109">
         <v>10000000</v>
       </c>
       <c r="C7" s="9">
@@ -9493,11 +9494,11 @@
       <c r="G7" s="13">
         <v>10000000</v>
       </c>
-      <c r="H7" s="106">
+      <c r="H7" s="113">
         <f t="shared" ref="H7:I7" si="0">AVERAGE(F7:F16)</f>
         <v>430.99737169999997</v>
       </c>
-      <c r="I7" s="108">
+      <c r="I7" s="115">
         <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
@@ -9510,17 +9511,17 @@
       <c r="L7" s="16">
         <v>86</v>
       </c>
-      <c r="M7" s="109">
+      <c r="M7" s="116">
         <f t="shared" ref="M7:N7" si="1">AVERAGE(K7:K16)</f>
         <v>1.1370000000000002E-2</v>
       </c>
-      <c r="N7" s="108">
+      <c r="N7" s="115">
         <f t="shared" si="1"/>
         <v>83.1</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="91"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="17">
         <v>2</v>
       </c>
@@ -9536,8 +9537,8 @@
       <c r="G8" s="21">
         <v>10000000</v>
       </c>
-      <c r="H8" s="99"/>
-      <c r="I8" s="91"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="98"/>
       <c r="J8" s="22">
         <v>-1</v>
       </c>
@@ -9547,11 +9548,11 @@
       <c r="L8" s="23">
         <v>82</v>
       </c>
-      <c r="M8" s="110"/>
-      <c r="N8" s="91"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="98"/>
     </row>
     <row r="9" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="91"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="24">
         <v>3</v>
       </c>
@@ -9567,8 +9568,8 @@
       <c r="G9" s="21">
         <v>10000000</v>
       </c>
-      <c r="H9" s="99"/>
-      <c r="I9" s="91"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="98"/>
       <c r="J9" s="22">
         <v>-1</v>
       </c>
@@ -9578,11 +9579,11 @@
       <c r="L9" s="27">
         <v>84</v>
       </c>
-      <c r="M9" s="110"/>
-      <c r="N9" s="91"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="98"/>
     </row>
     <row r="10" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="91"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="24">
         <v>4</v>
       </c>
@@ -9598,8 +9599,8 @@
       <c r="G10" s="31">
         <v>10000000</v>
       </c>
-      <c r="H10" s="99"/>
-      <c r="I10" s="91"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="98"/>
       <c r="J10" s="22">
         <v>-1</v>
       </c>
@@ -9609,11 +9610,11 @@
       <c r="L10" s="23">
         <v>83</v>
       </c>
-      <c r="M10" s="110"/>
-      <c r="N10" s="91"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="98"/>
     </row>
     <row r="11" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="91"/>
+      <c r="B11" s="98"/>
       <c r="C11" s="24">
         <v>5</v>
       </c>
@@ -9629,8 +9630,8 @@
       <c r="G11" s="21">
         <v>10000000</v>
       </c>
-      <c r="H11" s="99"/>
-      <c r="I11" s="91"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="98"/>
       <c r="J11" s="33">
         <v>-1</v>
       </c>
@@ -9640,11 +9641,11 @@
       <c r="L11" s="34">
         <v>83</v>
       </c>
-      <c r="M11" s="110"/>
-      <c r="N11" s="91"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="98"/>
     </row>
     <row r="12" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="86"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="24">
         <v>6</v>
       </c>
@@ -9660,8 +9661,8 @@
       <c r="G12" s="21">
         <v>10000000</v>
       </c>
-      <c r="H12" s="99"/>
-      <c r="I12" s="91"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="98"/>
       <c r="J12" s="22">
         <v>-1</v>
       </c>
@@ -9671,11 +9672,11 @@
       <c r="L12" s="23">
         <v>80</v>
       </c>
-      <c r="M12" s="110"/>
-      <c r="N12" s="91"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="98"/>
     </row>
     <row r="13" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="101" t="s">
+      <c r="B13" s="108" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="24">
@@ -9693,8 +9694,8 @@
       <c r="G13" s="21">
         <v>10000000</v>
       </c>
-      <c r="H13" s="99"/>
-      <c r="I13" s="91"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="98"/>
       <c r="J13" s="22">
         <v>-1</v>
       </c>
@@ -9704,11 +9705,11 @@
       <c r="L13" s="35">
         <v>83</v>
       </c>
-      <c r="M13" s="110"/>
-      <c r="N13" s="91"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="98"/>
     </row>
     <row r="14" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="91"/>
+      <c r="B14" s="98"/>
       <c r="C14" s="17">
         <v>8</v>
       </c>
@@ -9724,8 +9725,8 @@
       <c r="G14" s="21">
         <v>10000000</v>
       </c>
-      <c r="H14" s="99"/>
-      <c r="I14" s="91"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="98"/>
       <c r="J14" s="22">
         <v>-1</v>
       </c>
@@ -9735,11 +9736,11 @@
       <c r="L14" s="23">
         <v>84</v>
       </c>
-      <c r="M14" s="110"/>
-      <c r="N14" s="91"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="98"/>
     </row>
     <row r="15" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="91"/>
+      <c r="B15" s="98"/>
       <c r="C15" s="24">
         <v>9</v>
       </c>
@@ -9755,8 +9756,8 @@
       <c r="G15" s="21">
         <v>10000000</v>
       </c>
-      <c r="H15" s="99"/>
-      <c r="I15" s="91"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="98"/>
       <c r="J15" s="22">
         <v>-1</v>
       </c>
@@ -9766,11 +9767,11 @@
       <c r="L15" s="23">
         <v>82</v>
       </c>
-      <c r="M15" s="110"/>
-      <c r="N15" s="91"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="98"/>
     </row>
     <row r="16" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="92"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="37">
         <v>10</v>
       </c>
@@ -9786,8 +9787,8 @@
       <c r="G16" s="41">
         <v>10000000</v>
       </c>
-      <c r="H16" s="107"/>
-      <c r="I16" s="92"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="99"/>
       <c r="J16" s="42">
         <v>-1</v>
       </c>
@@ -9797,11 +9798,11 @@
       <c r="L16" s="35">
         <v>84</v>
       </c>
-      <c r="M16" s="111"/>
-      <c r="N16" s="92"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="99"/>
     </row>
     <row r="17" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="102">
+      <c r="B17" s="109">
         <v>100000000</v>
       </c>
       <c r="C17" s="43">
@@ -9819,10 +9820,10 @@
       <c r="G17" s="46">
         <v>100000000</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="95" t="s">
+      <c r="I17" s="102" t="s">
         <v>10</v>
       </c>
       <c r="J17" s="47">
@@ -9834,15 +9835,15 @@
       <c r="L17" s="46">
         <v>93</v>
       </c>
-      <c r="M17" s="93" t="s">
+      <c r="M17" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="N17" s="97" t="s">
+      <c r="N17" s="104" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="91"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="17">
         <v>2</v>
       </c>
@@ -9858,8 +9859,8 @@
       <c r="G18" s="23">
         <v>100000000</v>
       </c>
-      <c r="H18" s="94"/>
-      <c r="I18" s="96"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="103"/>
       <c r="J18" s="32">
         <v>-1</v>
       </c>
@@ -9869,11 +9870,11 @@
       <c r="L18" s="23">
         <v>90</v>
       </c>
-      <c r="M18" s="94"/>
-      <c r="N18" s="86"/>
+      <c r="M18" s="101"/>
+      <c r="N18" s="93"/>
     </row>
     <row r="19" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="91"/>
+      <c r="B19" s="98"/>
       <c r="C19" s="17">
         <v>3</v>
       </c>
@@ -9889,11 +9890,11 @@
       <c r="G19" s="23">
         <v>100000000</v>
       </c>
-      <c r="H19" s="112">
+      <c r="H19" s="119">
         <f t="shared" ref="H19:I19" si="2">H7*B17/B7</f>
         <v>4309.9737169999999</v>
       </c>
-      <c r="I19" s="98">
+      <c r="I19" s="105">
         <f t="shared" si="2"/>
         <v>10000000</v>
       </c>
@@ -9906,17 +9907,17 @@
       <c r="L19" s="23">
         <v>89</v>
       </c>
-      <c r="M19" s="87">
+      <c r="M19" s="94">
         <f t="shared" ref="M19:N19" si="3">M7*B17/B7</f>
         <v>0.11370000000000002</v>
       </c>
-      <c r="N19" s="90">
+      <c r="N19" s="97">
         <f t="shared" si="3"/>
         <v>83.1</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="91"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="17">
         <v>4</v>
       </c>
@@ -9932,8 +9933,8 @@
       <c r="G20" s="23">
         <v>100000000</v>
       </c>
-      <c r="H20" s="110"/>
-      <c r="I20" s="99"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="106"/>
       <c r="J20" s="32">
         <v>-1</v>
       </c>
@@ -9943,11 +9944,11 @@
       <c r="L20" s="23">
         <v>97</v>
       </c>
-      <c r="M20" s="88"/>
-      <c r="N20" s="91"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="98"/>
     </row>
     <row r="21" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="91"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="17">
         <v>5</v>
       </c>
@@ -9963,8 +9964,8 @@
       <c r="G21" s="23">
         <v>38334429</v>
       </c>
-      <c r="H21" s="96"/>
-      <c r="I21" s="100"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="107"/>
       <c r="J21" s="32">
         <v>38334428</v>
       </c>
@@ -9974,11 +9975,11 @@
       <c r="L21" s="23">
         <v>92</v>
       </c>
-      <c r="M21" s="94"/>
-      <c r="N21" s="86"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="86"/>
+      <c r="B22" s="93"/>
       <c r="C22" s="17">
         <v>6</v>
       </c>
@@ -9994,10 +9995,10 @@
       <c r="G22" s="23">
         <v>100000000</v>
       </c>
-      <c r="H22" s="113" t="s">
+      <c r="H22" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="114" t="s">
+      <c r="I22" s="121" t="s">
         <v>12</v>
       </c>
       <c r="J22" s="32">
@@ -10009,15 +10010,15 @@
       <c r="L22" s="23">
         <v>91</v>
       </c>
-      <c r="M22" s="113" t="s">
+      <c r="M22" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="85" t="s">
+      <c r="N22" s="92" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="101" t="s">
+      <c r="B23" s="108" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="17">
@@ -10035,8 +10036,8 @@
       <c r="G23" s="23">
         <v>40415748</v>
       </c>
-      <c r="H23" s="94"/>
-      <c r="I23" s="96"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="103"/>
       <c r="J23" s="32">
         <v>40415747</v>
       </c>
@@ -10046,11 +10047,11 @@
       <c r="L23" s="23">
         <v>82</v>
       </c>
-      <c r="M23" s="94"/>
-      <c r="N23" s="86"/>
+      <c r="M23" s="101"/>
+      <c r="N23" s="93"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="91"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="17">
         <v>8</v>
       </c>
@@ -10066,11 +10067,11 @@
       <c r="G24" s="23">
         <v>100000000</v>
       </c>
-      <c r="H24" s="115">
+      <c r="H24" s="122">
         <f t="shared" ref="H24:I24" si="4">AVERAGE(F17:F26)</f>
         <v>4121.3880300000001</v>
       </c>
-      <c r="I24" s="98">
+      <c r="I24" s="105">
         <f t="shared" si="4"/>
         <v>87875017.700000003</v>
       </c>
@@ -10083,17 +10084,17 @@
       <c r="L24" s="23">
         <v>96</v>
       </c>
-      <c r="M24" s="87">
+      <c r="M24" s="94">
         <f t="shared" ref="M24:N24" si="5">AVERAGE(K17:K26)</f>
         <v>1.3420000000000001E-2</v>
       </c>
-      <c r="N24" s="90">
+      <c r="N24" s="97">
         <f t="shared" si="5"/>
         <v>91.1</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="91"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="17">
         <v>9</v>
       </c>
@@ -10109,8 +10110,8 @@
       <c r="G25" s="23">
         <v>100000000</v>
       </c>
-      <c r="H25" s="88"/>
-      <c r="I25" s="99"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="106"/>
       <c r="J25" s="32">
         <v>-1</v>
       </c>
@@ -10120,11 +10121,11 @@
       <c r="L25" s="23">
         <v>91</v>
       </c>
-      <c r="M25" s="88"/>
-      <c r="N25" s="91"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="98"/>
     </row>
     <row r="26" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="92"/>
+      <c r="B26" s="99"/>
       <c r="C26" s="50">
         <v>10</v>
       </c>
@@ -10140,8 +10141,8 @@
       <c r="G26" s="41">
         <v>100000000</v>
       </c>
-      <c r="H26" s="89"/>
-      <c r="I26" s="107"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="114"/>
       <c r="J26" s="51">
         <v>-1</v>
       </c>
@@ -10151,8 +10152,8 @@
       <c r="L26" s="41">
         <v>90</v>
       </c>
-      <c r="M26" s="89"/>
-      <c r="N26" s="92"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="99"/>
     </row>
     <row r="27" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11176,56 +11177,56 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:24" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="118">
+      <c r="E3" s="88"/>
+      <c r="F3" s="89">
         <v>10000</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="118" t="s">
+      <c r="G3" s="88"/>
+      <c r="H3" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="119"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="90"/>
     </row>
     <row r="4" spans="2:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120" t="s">
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="120" t="s">
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="119"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="90"/>
     </row>
     <row r="5" spans="2:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53" t="s">
@@ -11745,124 +11746,124 @@
       </c>
     </row>
     <row r="13" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="123">
+      <c r="D13" s="33">
         <v>11.51</v>
       </c>
-      <c r="E13" s="123">
+      <c r="E13" s="33">
         <v>10.51</v>
       </c>
-      <c r="F13" s="123">
+      <c r="F13" s="33">
         <v>12.01</v>
       </c>
-      <c r="G13" s="123">
+      <c r="G13" s="33">
         <v>11.01</v>
       </c>
-      <c r="H13" s="123">
+      <c r="H13" s="33">
         <v>12.67</v>
       </c>
-      <c r="I13" s="122">
+      <c r="I13" s="86">
         <f>AVERAGE(C13:H13)</f>
         <v>11.542</v>
       </c>
-      <c r="J13" s="123">
+      <c r="J13" s="33">
         <v>153150</v>
       </c>
-      <c r="K13" s="123">
+      <c r="K13" s="33">
         <v>148262</v>
       </c>
-      <c r="L13" s="123">
+      <c r="L13" s="33">
         <v>153651</v>
       </c>
-      <c r="M13" s="123">
+      <c r="M13" s="33">
         <v>165279</v>
       </c>
-      <c r="N13" s="123">
+      <c r="N13" s="33">
         <v>179295</v>
       </c>
-      <c r="O13" s="122">
+      <c r="O13" s="86">
         <f t="shared" si="1"/>
         <v>159927.4</v>
       </c>
-      <c r="P13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="Q13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="R13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="S13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="T13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="U13" s="122">
+      <c r="P13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="R13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="S13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="T13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="U13" s="86">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="15" spans="2:24" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="118">
+      <c r="E15" s="88"/>
+      <c r="F15" s="89">
         <v>20000</v>
       </c>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118" t="s">
+      <c r="G15" s="88"/>
+      <c r="H15" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="119"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="90"/>
     </row>
     <row r="16" spans="2:24" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="120" t="s">
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="120" t="s">
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="117"/>
-      <c r="T16" s="117"/>
-      <c r="U16" s="117"/>
-      <c r="V16" s="117"/>
-      <c r="W16" s="117"/>
-      <c r="X16" s="119"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="90"/>
     </row>
     <row r="17" spans="2:24" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B17" s="53" t="s">
@@ -12008,7 +12009,7 @@
         <v>301981446</v>
       </c>
       <c r="X18" s="70">
-        <f t="shared" ref="X18:X25" si="5">AVERAGE(S18:W18)</f>
+        <f t="shared" ref="X18:X24" si="5">AVERAGE(S18:W18)</f>
         <v>299743746.60000002</v>
       </c>
     </row>
@@ -12475,12 +12476,15 @@
       </c>
     </row>
     <row r="25" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="85" t="s">
         <v>46</v>
       </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
       <c r="D25">
-        <f>I13*(F15/F3)</f>
-        <v>23.084</v>
+        <f>I13*(F15*LOG(F15,2))/(F3*LOG(F3,2))</f>
+        <v>24.821244104976834</v>
       </c>
       <c r="E25">
         <v>25.52</v>
@@ -12520,32 +12524,32 @@
       <c r="P25">
         <v>333296</v>
       </c>
-      <c r="Q25" s="122">
+      <c r="Q25" s="86">
         <f>AVERAGE(L25:P25)</f>
         <v>332337.2</v>
       </c>
       <c r="R25">
         <f>U13*(F15*LOG(F15,2))/(F3*LOG(F3,2))</f>
-        <v>43010.299956639807</v>
+        <v>21505.149978319903</v>
       </c>
       <c r="S25">
-        <v>40000</v>
-      </c>
-      <c r="T25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="U25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="V25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="W25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="X25" s="122">
+        <v>20000</v>
+      </c>
+      <c r="T25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="U25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="V25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="W25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="X25" s="86">
         <f>AVERAGE(S25:W25)</f>
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="26" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13851,56 +13855,56 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:24" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="118">
+      <c r="E3" s="88"/>
+      <c r="F3" s="89">
         <v>10000</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="118" t="s">
+      <c r="G3" s="88"/>
+      <c r="H3" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="119"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="90"/>
     </row>
     <row r="4" spans="2:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120" t="s">
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="120" t="s">
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="119"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="90"/>
     </row>
     <row r="5" spans="2:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53" t="s">
@@ -14420,8 +14424,11 @@
       </c>
     </row>
     <row r="13" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="85" t="s">
         <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
       </c>
       <c r="D13">
         <v>826.11</v>
@@ -14438,7 +14445,7 @@
       <c r="H13">
         <v>803.87</v>
       </c>
-      <c r="I13" s="122">
+      <c r="I13" s="86">
         <f>AVERAGE(D13:H13)</f>
         <v>818.96</v>
       </c>
@@ -14457,88 +14464,88 @@
       <c r="N13">
         <v>17871454</v>
       </c>
-      <c r="O13" s="122">
+      <c r="O13" s="86">
         <f>AVERAGE(J13:N13)</f>
         <v>18525493.399999999</v>
       </c>
-      <c r="P13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="Q13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="R13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="S13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="T13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="U13" s="122">
+      <c r="P13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="R13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="S13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="T13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="U13" s="86">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:24" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="118">
+      <c r="E15" s="88"/>
+      <c r="F15" s="89">
         <v>20000</v>
       </c>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118" t="s">
+      <c r="G15" s="88"/>
+      <c r="H15" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="119"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="90"/>
     </row>
     <row r="16" spans="2:24" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="120" t="s">
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="120" t="s">
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="117"/>
-      <c r="T16" s="117"/>
-      <c r="U16" s="117"/>
-      <c r="V16" s="117"/>
-      <c r="W16" s="117"/>
-      <c r="X16" s="119"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="90"/>
     </row>
     <row r="17" spans="2:24" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B17" s="53" t="s">
@@ -14661,7 +14668,7 @@
         <v>779220</v>
       </c>
       <c r="Q18" s="70">
-        <f t="shared" ref="Q18:Q24" si="4">AVERAGE(L18:P18)</f>
+        <f t="shared" ref="Q18:Q23" si="4">AVERAGE(L18:P18)</f>
         <v>819090.4</v>
       </c>
       <c r="R18" s="71">
@@ -14684,7 +14691,7 @@
         <v>113376</v>
       </c>
       <c r="X18" s="70">
-        <f t="shared" ref="X18:X25" si="5">AVERAGE(S18:W18)</f>
+        <f t="shared" ref="X18:X24" si="5">AVERAGE(S18:W18)</f>
         <v>110527.8</v>
       </c>
     </row>
@@ -15151,77 +15158,80 @@
       </c>
     </row>
     <row r="25" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="85" t="s">
         <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
       </c>
       <c r="D25">
         <f>I13*(F15/F3)</f>
         <v>1637.92</v>
       </c>
-      <c r="E25" s="124">
+      <c r="E25" s="29">
         <v>3596.86</v>
       </c>
-      <c r="F25" s="124">
+      <c r="F25" s="29">
         <v>3649.38</v>
       </c>
-      <c r="G25" s="124">
+      <c r="G25" s="29">
         <v>3755.36</v>
       </c>
-      <c r="H25" s="124">
+      <c r="H25" s="29">
         <v>3787.48</v>
       </c>
-      <c r="I25" s="124">
+      <c r="I25" s="29">
         <v>3711.42</v>
       </c>
-      <c r="J25" s="122">
+      <c r="J25" s="86">
         <f t="shared" si="3"/>
         <v>3700.1</v>
       </c>
       <c r="K25">
-        <f>O13*(F15*LOG(F15,2))/(F3*LOG(F3,2))</f>
-        <v>39839351.398937553</v>
-      </c>
-      <c r="L25" s="124">
+        <f>ROUND(O13*F15*LOG(F15) / (F3*LOG(F3)),0)</f>
+        <v>39839351</v>
+      </c>
+      <c r="L25" s="29">
         <v>73304137</v>
       </c>
-      <c r="M25" s="124">
+      <c r="M25" s="29">
         <v>73380969</v>
       </c>
-      <c r="N25" s="124">
+      <c r="N25" s="29">
         <v>73397272</v>
       </c>
-      <c r="O25" s="124">
+      <c r="O25" s="29">
         <v>73506057</v>
       </c>
-      <c r="P25" s="124">
+      <c r="P25" s="29">
         <v>73147649</v>
       </c>
-      <c r="Q25" s="122">
+      <c r="Q25" s="86">
         <f>AVERAGE(L25:P25)</f>
         <v>73347216.799999997</v>
       </c>
       <c r="R25">
-        <f>U13*(F15/F3)</f>
-        <v>40000</v>
-      </c>
-      <c r="S25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="T25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="U25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="V25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="W25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="X25" s="122">
+        <f>ROUND(U13*F15*LOG(F15) / (F3*LOG(F3)),0)</f>
+        <v>21505</v>
+      </c>
+      <c r="S25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="T25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="U25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="V25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="W25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="X25" s="86">
         <f>AVERAGE(S25:W25)</f>
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="26" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16864,56 +16874,56 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:24" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="118">
+      <c r="E3" s="88"/>
+      <c r="F3" s="89">
         <v>10000</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="118" t="s">
+      <c r="G3" s="88"/>
+      <c r="H3" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="119"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="90"/>
     </row>
     <row r="4" spans="2:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="120" t="s">
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="120" t="s">
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="119"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="90"/>
     </row>
     <row r="5" spans="2:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53" t="s">
@@ -17000,7 +17010,7 @@
         <v>5499.41</v>
       </c>
       <c r="I6" s="46">
-        <f t="shared" ref="I6:I13" si="0">AVERAGE(D6:H6)</f>
+        <f t="shared" ref="I6:I12" si="0">AVERAGE(D6:H6)</f>
         <v>5529.6760000000004</v>
       </c>
       <c r="J6" s="60">
@@ -17433,124 +17443,127 @@
       </c>
     </row>
     <row r="13" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="123">
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="33">
         <v>704.15</v>
       </c>
-      <c r="E13" s="123">
+      <c r="E13" s="33">
         <v>748.42</v>
       </c>
-      <c r="F13" s="123">
+      <c r="F13" s="33">
         <v>717.31</v>
       </c>
-      <c r="G13" s="123">
+      <c r="G13" s="33">
         <v>729.01</v>
       </c>
-      <c r="H13" s="123">
+      <c r="H13" s="33">
         <v>743.9</v>
       </c>
-      <c r="I13" s="122">
+      <c r="I13" s="86">
         <f>AVERAGE(D13:H13)</f>
         <v>728.55800000000011</v>
       </c>
-      <c r="J13" s="123">
+      <c r="J13" s="33">
         <v>15413728</v>
       </c>
-      <c r="K13" s="123">
+      <c r="K13" s="33">
         <v>16008127</v>
       </c>
-      <c r="L13" s="123">
+      <c r="L13" s="33">
         <v>15601173</v>
       </c>
-      <c r="M13" s="123">
+      <c r="M13" s="33">
         <v>15738508</v>
       </c>
-      <c r="N13" s="123">
+      <c r="N13" s="33">
         <v>15917318</v>
       </c>
-      <c r="O13" s="122">
+      <c r="O13" s="86">
         <f t="shared" si="1"/>
         <v>15735770.800000001</v>
       </c>
-      <c r="P13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="Q13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="R13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="S13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="T13" s="123">
-        <v>20000</v>
-      </c>
-      <c r="U13" s="122">
+      <c r="P13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="R13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="S13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="T13" s="33">
+        <v>10000</v>
+      </c>
+      <c r="U13" s="86">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="15" spans="2:24" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="118">
+      <c r="E15" s="88"/>
+      <c r="F15" s="89">
         <v>20000</v>
       </c>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118" t="s">
+      <c r="G15" s="88"/>
+      <c r="H15" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="119"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="90"/>
     </row>
     <row r="16" spans="2:24" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="120" t="s">
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="120" t="s">
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="117"/>
-      <c r="T16" s="117"/>
-      <c r="U16" s="117"/>
-      <c r="V16" s="117"/>
-      <c r="W16" s="117"/>
-      <c r="X16" s="119"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="90"/>
     </row>
     <row r="17" spans="2:24" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B17" s="53" t="s">
@@ -18163,12 +18176,15 @@
       </c>
     </row>
     <row r="25" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="85" t="s">
         <v>46</v>
       </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
       <c r="D25">
-        <f>I13*(F15/F3)</f>
-        <v>1457.1160000000002</v>
+        <f>ROUND(I13*F15*LOG(F15) / (F3*LOG(F3)),0)</f>
+        <v>1567</v>
       </c>
       <c r="E25">
         <v>3420.58</v>
@@ -18185,55 +18201,55 @@
       <c r="I25">
         <v>3337.16</v>
       </c>
-      <c r="J25" s="122">
+      <c r="J25" s="86">
         <f>AVERAGE(E25:I25)</f>
         <v>3655.0680000000002</v>
       </c>
       <c r="K25">
-        <f>O13*(F15*LOG(F15,2))/(F3*LOG(F3,2))</f>
-        <v>33840011.1078467</v>
-      </c>
-      <c r="L25" s="124">
+        <f>ROUND(O13*F15*LOG(F15) / (F3*LOG(F3)),0)</f>
+        <v>33840011</v>
+      </c>
+      <c r="L25" s="29">
         <v>63518856</v>
       </c>
-      <c r="M25" s="124">
+      <c r="M25" s="29">
         <v>63100176</v>
       </c>
-      <c r="N25" s="124">
+      <c r="N25" s="29">
         <v>64282889</v>
       </c>
-      <c r="O25" s="124">
+      <c r="O25" s="29">
         <v>63677736</v>
       </c>
-      <c r="P25" s="124">
+      <c r="P25" s="29">
         <v>62851539</v>
       </c>
-      <c r="Q25" s="122">
+      <c r="Q25" s="86">
         <f t="shared" si="4"/>
         <v>63486239.200000003</v>
       </c>
       <c r="R25">
-        <f>U13*(F15*LOG(F15,2))/(F3*LOG(F3,2))</f>
-        <v>43010.299956639807</v>
-      </c>
-      <c r="S25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="T25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="U25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="V25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="W25" s="124">
-        <v>40000</v>
-      </c>
-      <c r="X25" s="122">
+        <f>ROUND(U13*F15*LOG(F15) / (F3*LOG(F3)),0)</f>
+        <v>21505</v>
+      </c>
+      <c r="S25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="T25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="U25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="V25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="W25" s="29">
+        <v>20000</v>
+      </c>
+      <c r="X25" s="86">
         <f t="shared" si="5"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="26" spans="2:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
